--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
   <si>
     <t>Record</t>
   </si>
@@ -39,157 +39,127 @@
     <t>Chill YNs</t>
   </si>
   <si>
+    <t>Yung Killas</t>
+  </si>
+  <si>
+    <t>Tailed Bijan Bomb</t>
+  </si>
+  <si>
     <t>Ross' Sauces</t>
   </si>
   <si>
-    <t>Yung Killas</t>
-  </si>
-  <si>
     <t>Penguins FC</t>
   </si>
   <si>
     <t>big beautiful lugia</t>
   </si>
   <si>
-    <t>Tailed Bijan Bomb</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>98.5%</t>
-  </si>
-  <si>
-    <t>96.3%</t>
-  </si>
-  <si>
-    <t>92.6%</t>
-  </si>
-  <si>
-    <t>66.5%</t>
-  </si>
-  <si>
-    <t>33.4%</t>
-  </si>
-  <si>
-    <t>13.3%</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>92.3%</t>
+  </si>
+  <si>
+    <t>48.2%</t>
+  </si>
+  <si>
+    <t>35.8%</t>
+  </si>
+  <si>
+    <t>24.0%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-6567</t>
-  </si>
-  <si>
-    <t>-2603</t>
-  </si>
-  <si>
-    <t>-1251</t>
-  </si>
-  <si>
-    <t>-199</t>
-  </si>
-  <si>
-    <t>+199</t>
-  </si>
-  <si>
-    <t>+652</t>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-1199</t>
+  </si>
+  <si>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+179</t>
+  </si>
+  <si>
+    <t>+317</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>55.3%</t>
-  </si>
-  <si>
-    <t>29.6%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>76.8%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-124</t>
-  </si>
-  <si>
-    <t>+238</t>
-  </si>
-  <si>
-    <t>+1251</t>
-  </si>
-  <si>
-    <t>+2122</t>
-  </si>
-  <si>
-    <t>+3233</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>-331</t>
+  </si>
+  <si>
+    <t>+421</t>
+  </si>
+  <si>
+    <t>+4248</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>62.6%</t>
-  </si>
-  <si>
-    <t>25.6%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>-167</t>
-  </si>
-  <si>
-    <t>+291</t>
-  </si>
-  <si>
-    <t>+975</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>43.0%</t>
+  </si>
+  <si>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>24.9%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>+133</t>
+  </si>
+  <si>
+    <t>+239</t>
+  </si>
+  <si>
+    <t>+302</t>
+  </si>
+  <si>
+    <t>+3746</t>
   </si>
 </sst>
 </file>
@@ -572,10 +542,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -583,13 +553,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,10 +570,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,10 +584,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -628,10 +598,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,13 +609,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -653,13 +623,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,13 +637,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -708,10 +678,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -719,13 +689,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -736,10 +706,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -750,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -764,10 +734,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -775,41 +745,41 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -841,13 +811,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -855,13 +825,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -869,13 +839,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -886,66 +856,66 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
   <si>
     <t>Record</t>
   </si>
@@ -33,37 +33,37 @@
     <t>Yvng Killas</t>
   </si>
   <si>
+    <t>Chill YNs</t>
+  </si>
+  <si>
     <t>Chase Ball. Touchdown!</t>
   </si>
   <si>
-    <t>Chill YNs</t>
-  </si>
-  <si>
     <t>Yung Killas</t>
   </si>
   <si>
     <t>Tailed Bijan Bomb</t>
   </si>
   <si>
+    <t>big beautiful lugia</t>
+  </si>
+  <si>
+    <t>Penguins FC</t>
+  </si>
+  <si>
     <t>Ross' Sauces</t>
   </si>
   <si>
-    <t>Penguins FC</t>
-  </si>
-  <si>
-    <t>big beautiful lugia</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
   </si>
   <si>
     <t>100.0%</t>
@@ -72,16 +72,19 @@
     <t>99.7%</t>
   </si>
   <si>
-    <t>92.3%</t>
-  </si>
-  <si>
-    <t>48.2%</t>
-  </si>
-  <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>24.0%</t>
+    <t>94.7%</t>
+  </si>
+  <si>
+    <t>65.2%</t>
+  </si>
+  <si>
+    <t>63.0%</t>
+  </si>
+  <si>
+    <t>56.7%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
   </si>
   <si>
     <t>-99900</t>
@@ -90,31 +93,34 @@
     <t>-33233</t>
   </si>
   <si>
-    <t>-1199</t>
-  </si>
-  <si>
-    <t>+107</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+317</t>
+    <t>-1787</t>
+  </si>
+  <si>
+    <t>-187</t>
+  </si>
+  <si>
+    <t>-170</t>
+  </si>
+  <si>
+    <t>-131</t>
+  </si>
+  <si>
+    <t>+383</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>76.8%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
+    <t>81.6%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -123,43 +129,49 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-331</t>
-  </si>
-  <si>
-    <t>+421</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>-443</t>
+  </si>
+  <si>
+    <t>+641</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>43.0%</t>
-  </si>
-  <si>
-    <t>29.5%</t>
-  </si>
-  <si>
-    <t>24.9%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>+133</t>
-  </si>
-  <si>
-    <t>+239</t>
-  </si>
-  <si>
-    <t>+302</t>
-  </si>
-  <si>
-    <t>+3746</t>
+    <t>60.4%</t>
+  </si>
+  <si>
+    <t>14.4%</t>
+  </si>
+  <si>
+    <t>14.0%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>-153</t>
+  </si>
+  <si>
+    <t>+594</t>
+  </si>
+  <si>
+    <t>+614</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+8991</t>
   </si>
 </sst>
 </file>
@@ -545,7 +557,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -553,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -567,13 +579,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -584,10 +596,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -598,10 +610,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -609,13 +621,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -623,13 +635,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -640,10 +652,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -678,10 +690,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -689,13 +701,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -703,13 +715,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -720,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -734,24 +746,24 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -759,27 +771,27 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -814,10 +826,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -825,13 +837,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -839,13 +851,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -856,38 +868,38 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -895,27 +907,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
   <si>
     <t>Record</t>
   </si>
@@ -33,145 +33,136 @@
     <t>Yvng Killas</t>
   </si>
   <si>
+    <t>Chase Ball. Touchdown!</t>
+  </si>
+  <si>
     <t>Chill YNs</t>
   </si>
   <si>
-    <t>Chase Ball. Touchdown!</t>
-  </si>
-  <si>
     <t>Yung Killas</t>
   </si>
   <si>
+    <t>Penguins FC</t>
+  </si>
+  <si>
+    <t>big beautiful lugia</t>
+  </si>
+  <si>
     <t>Tailed Bijan Bomb</t>
   </si>
   <si>
-    <t>big beautiful lugia</t>
-  </si>
-  <si>
-    <t>Penguins FC</t>
-  </si>
-  <si>
     <t>Ross' Sauces</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>94.7%</t>
-  </si>
-  <si>
-    <t>65.2%</t>
-  </si>
-  <si>
-    <t>63.0%</t>
-  </si>
-  <si>
-    <t>56.7%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>98.8%</t>
+  </si>
+  <si>
+    <t>79.3%</t>
+  </si>
+  <si>
+    <t>56.9%</t>
+  </si>
+  <si>
+    <t>47.0%</t>
+  </si>
+  <si>
+    <t>18.1%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-1787</t>
-  </si>
-  <si>
-    <t>-187</t>
-  </si>
-  <si>
-    <t>-170</t>
-  </si>
-  <si>
-    <t>-131</t>
-  </si>
-  <si>
-    <t>+383</t>
+    <t>-8233</t>
+  </si>
+  <si>
+    <t>-383</t>
+  </si>
+  <si>
+    <t>-132</t>
+  </si>
+  <si>
+    <t>+113</t>
+  </si>
+  <si>
+    <t>+452</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>81.6%</t>
-  </si>
-  <si>
-    <t>13.5%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-443</t>
-  </si>
-  <si>
-    <t>+641</t>
-  </si>
-  <si>
-    <t>+2173</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>-269</t>
+  </si>
+  <si>
+    <t>+545</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+19900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>60.4%</t>
-  </si>
-  <si>
-    <t>14.4%</t>
-  </si>
-  <si>
-    <t>14.0%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>-153</t>
-  </si>
-  <si>
-    <t>+594</t>
-  </si>
-  <si>
-    <t>+614</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+8991</t>
+    <t>61.0%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
+  </si>
+  <si>
+    <t>15.9%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>-156</t>
+  </si>
+  <si>
+    <t>+424</t>
+  </si>
+  <si>
+    <t>+529</t>
+  </si>
+  <si>
+    <t>+2400</t>
   </si>
 </sst>
 </file>
@@ -554,10 +545,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -565,13 +556,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -579,10 +570,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -596,7 +587,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -607,10 +598,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -621,10 +612,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -635,10 +626,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -649,10 +640,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -693,7 +684,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -701,13 +692,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -715,13 +706,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -735,35 +726,35 @@
         <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -771,13 +762,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -785,13 +776,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -823,13 +814,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -837,13 +828,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -851,13 +842,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -865,41 +856,41 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -907,27 +898,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
   <si>
     <t>Record</t>
   </si>
@@ -33,136 +33,151 @@
     <t>Yvng Killas</t>
   </si>
   <si>
+    <t>Chill YNs</t>
+  </si>
+  <si>
+    <t>Yung Killas</t>
+  </si>
+  <si>
     <t>Chase Ball. Touchdown!</t>
   </si>
   <si>
-    <t>Chill YNs</t>
-  </si>
-  <si>
-    <t>Yung Killas</t>
-  </si>
-  <si>
     <t>Penguins FC</t>
   </si>
   <si>
+    <t>Tailed Bijan Bomb</t>
+  </si>
+  <si>
+    <t>Ross' Sauces</t>
+  </si>
+  <si>
     <t>big beautiful lugia</t>
   </si>
   <si>
-    <t>Tailed Bijan Bomb</t>
-  </si>
-  <si>
-    <t>Ross' Sauces</t>
-  </si>
-  <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>98.8%</t>
-  </si>
-  <si>
-    <t>79.3%</t>
-  </si>
-  <si>
-    <t>56.9%</t>
-  </si>
-  <si>
-    <t>47.0%</t>
-  </si>
-  <si>
-    <t>18.1%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>98.2%</t>
+  </si>
+  <si>
+    <t>95.5%</t>
+  </si>
+  <si>
+    <t>52.3%</t>
+  </si>
+  <si>
+    <t>41.1%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-8233</t>
-  </si>
-  <si>
-    <t>-383</t>
-  </si>
-  <si>
-    <t>-132</t>
-  </si>
-  <si>
-    <t>+113</t>
-  </si>
-  <si>
-    <t>+452</t>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-5456</t>
+  </si>
+  <si>
+    <t>-2122</t>
+  </si>
+  <si>
+    <t>-110</t>
+  </si>
+  <si>
+    <t>+143</t>
+  </si>
+  <si>
+    <t>+641</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>72.9%</t>
-  </si>
-  <si>
-    <t>15.5%</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>75.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>5.2%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-269</t>
-  </si>
-  <si>
-    <t>+545</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>-313</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+1120</t>
+  </si>
+  <si>
+    <t>+1823</t>
+  </si>
+  <si>
+    <t>+8233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>19.1%</t>
-  </si>
-  <si>
-    <t>15.9%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>-156</t>
-  </si>
-  <si>
-    <t>+424</t>
-  </si>
-  <si>
-    <t>+529</t>
-  </si>
-  <si>
-    <t>+2400</t>
+    <t>62.0%</t>
+  </si>
+  <si>
+    <t>22.6%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-163</t>
+  </si>
+  <si>
+    <t>+342</t>
+  </si>
+  <si>
+    <t>+576</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -548,7 +563,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -559,10 +574,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -570,13 +585,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -584,13 +599,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -601,10 +616,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -615,10 +630,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -626,13 +641,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -643,10 +658,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -681,10 +696,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -695,10 +710,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -706,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -720,69 +735,69 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -817,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -828,13 +843,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -845,80 +860,80 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
   <si>
     <t>Record</t>
   </si>
@@ -54,130 +54,133 @@
     <t>big beautiful lugia</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>98.2%</t>
-  </si>
-  <si>
-    <t>95.5%</t>
-  </si>
-  <si>
-    <t>52.3%</t>
-  </si>
-  <si>
-    <t>41.1%</t>
-  </si>
-  <si>
-    <t>13.5%</t>
+    <t>97.2%</t>
+  </si>
+  <si>
+    <t>89.7%</t>
+  </si>
+  <si>
+    <t>88.6%</t>
+  </si>
+  <si>
+    <t>61.4%</t>
+  </si>
+  <si>
+    <t>45.3%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-5456</t>
-  </si>
-  <si>
-    <t>-2122</t>
-  </si>
-  <si>
-    <t>-110</t>
-  </si>
-  <si>
-    <t>+143</t>
-  </si>
-  <si>
-    <t>+641</t>
+    <t>-3471</t>
+  </si>
+  <si>
+    <t>-871</t>
+  </si>
+  <si>
+    <t>-777</t>
+  </si>
+  <si>
+    <t>-159</t>
+  </si>
+  <si>
+    <t>+121</t>
+  </si>
+  <si>
+    <t>+462</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>75.8%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>5.2%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>34.5%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-313</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+1120</t>
-  </si>
-  <si>
-    <t>+1823</t>
-  </si>
-  <si>
-    <t>+8233</t>
+    <t>-155</t>
+  </si>
+  <si>
+    <t>+190</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>+11011</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>62.0%</t>
-  </si>
-  <si>
-    <t>22.6%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-163</t>
-  </si>
-  <si>
-    <t>+342</t>
-  </si>
-  <si>
-    <t>+576</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>58.6%</t>
+  </si>
+  <si>
+    <t>23.8%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>-142</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+687</t>
+  </si>
+  <si>
+    <t>+3900</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -560,10 +563,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -571,13 +574,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -588,10 +591,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -602,10 +605,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -616,10 +619,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -627,13 +630,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -641,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -655,13 +658,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -696,10 +699,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -707,13 +710,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -724,10 +727,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -738,10 +741,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -752,10 +755,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -763,13 +766,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -777,13 +780,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -791,13 +794,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -829,13 +832,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -843,13 +846,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -857,38 +860,38 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -896,44 +899,44 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
+++ b/data/odds/Ross' Fantasy League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>Record</t>
   </si>
@@ -39,12 +39,12 @@
     <t>Yung Killas</t>
   </si>
   <si>
+    <t>Penguins FC</t>
+  </si>
+  <si>
     <t>Chase Ball. Touchdown!</t>
   </si>
   <si>
-    <t>Penguins FC</t>
-  </si>
-  <si>
     <t>Tailed Bijan Bomb</t>
   </si>
   <si>
@@ -69,118 +69,121 @@
     <t>100.0%</t>
   </si>
   <si>
-    <t>97.2%</t>
-  </si>
-  <si>
-    <t>89.7%</t>
-  </si>
-  <si>
-    <t>88.6%</t>
-  </si>
-  <si>
-    <t>61.4%</t>
-  </si>
-  <si>
-    <t>45.3%</t>
-  </si>
-  <si>
-    <t>17.8%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>97.3%</t>
+  </si>
+  <si>
+    <t>88.9%</t>
+  </si>
+  <si>
+    <t>88.5%</t>
+  </si>
+  <si>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>45.2%</t>
+  </si>
+  <si>
+    <t>17.9%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-3471</t>
-  </si>
-  <si>
-    <t>-871</t>
-  </si>
-  <si>
-    <t>-777</t>
-  </si>
-  <si>
-    <t>-159</t>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-3604</t>
+  </si>
+  <si>
+    <t>-801</t>
+  </si>
+  <si>
+    <t>-770</t>
+  </si>
+  <si>
+    <t>-166</t>
   </si>
   <si>
     <t>+121</t>
   </si>
   <si>
-    <t>+462</t>
+    <t>+459</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>60.8%</t>
-  </si>
-  <si>
-    <t>34.5%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
+    <t>59.3%</t>
+  </si>
+  <si>
+    <t>35.5%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-155</t>
-  </si>
-  <si>
-    <t>+190</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+8991</t>
-  </si>
-  <si>
-    <t>+11011</t>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+182</t>
+  </si>
+  <si>
+    <t>+3746</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+8233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>58.6%</t>
-  </si>
-  <si>
-    <t>23.8%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-142</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+687</t>
-  </si>
-  <si>
-    <t>+3900</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>24.2%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+313</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+3233</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -566,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -577,10 +580,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -591,10 +594,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -602,13 +605,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -616,13 +619,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -633,10 +636,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -647,10 +650,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -661,10 +664,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -685,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -699,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -713,10 +716,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -727,38 +730,38 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -769,10 +772,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -783,10 +786,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -797,10 +800,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -835,10 +838,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -849,10 +852,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -863,38 +866,38 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -905,10 +908,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -919,10 +922,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -933,10 +936,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
